--- a/survey_templates/031_study_app_setup_survey--survey_templates.xlsx
+++ b/survey_templates/031_study_app_setup_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1056,8 +1056,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_11,_'name':_'option1',_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 11, 'name': 'option1', 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_12,_'name':_'option2',_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 12, 'name': 'option2', 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1119,12 +1119,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_13,_'name':_'option1',_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 13, 'name': 'option1', 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1136,12 +1136,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_14,_'name':_'option2',_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 14, 'name': 'option2', 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1153,12 +1153,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_15,_'name':_'option3',_'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 15, 'name': 'option3', 'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1204,12 +1204,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_21,_'name':_'option1_2',_'label':_'option_1_2'}</t>
+          <t>option_1_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 21, 'name': 'option1_2', 'label': 'Option 1 2'}</t>
+          <t>Option 1 2</t>
         </is>
       </c>
     </row>
@@ -1221,12 +1221,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_22,_'name':_'option2_2',_'label':_'option_2_2'}</t>
+          <t>option_2_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 22, 'name': 'option2_2', 'label': 'Option 2 2'}</t>
+          <t>Option 2 2</t>
         </is>
       </c>
     </row>
@@ -1238,12 +1238,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_23,_'name':_'option1_3',_'label':_'option_1_3'}</t>
+          <t>option_1_3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 23, 'name': 'option1_3', 'label': 'Option 1 3'}</t>
+          <t>Option 1 3</t>
         </is>
       </c>
     </row>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_24,_'name':_'option2_3',_'label':_'option_2_3'}</t>
+          <t>option_2_3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 24, 'name': 'option2_3', 'label': 'Option 2 3'}</t>
+          <t>Option 2 3</t>
         </is>
       </c>
     </row>
